--- a/output/CS_SFIAFormat/sfiaformat_mapping_cosine_SkillNER YAKE_CS.xlsx
+++ b/output/CS_SFIAFormat/sfiaformat_mapping_cosine_SkillNER YAKE_CS.xlsx
@@ -516,7 +516,7 @@
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="n">
-        <v>0.2117</v>
+        <v>0.2481</v>
       </c>
       <c r="H4" t="inlineStr"/>
     </row>
@@ -531,10 +531,10 @@
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>0.2102</v>
+        <v>0.2547</v>
       </c>
       <c r="G5" t="n">
-        <v>0.225</v>
+        <v>0.2258</v>
       </c>
       <c r="H5" t="inlineStr"/>
     </row>
@@ -586,7 +586,7 @@
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="n">
-        <v>0.2058</v>
+        <v>0.2066</v>
       </c>
       <c r="H8" t="inlineStr"/>
     </row>
@@ -628,13 +628,13 @@
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="n">
-        <v>0.2461</v>
+        <v>0.293</v>
       </c>
       <c r="F11" t="n">
         <v>0.2692</v>
       </c>
       <c r="G11" t="n">
-        <v>0.2129</v>
+        <v>0.2667</v>
       </c>
       <c r="H11" t="inlineStr"/>
     </row>
@@ -688,19 +688,19 @@
       </c>
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="n">
-        <v>0.2201</v>
+        <v>0.2553</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2009</v>
+        <v>0.2368</v>
       </c>
       <c r="E15" t="n">
-        <v>0.2302</v>
+        <v>0.2804</v>
       </c>
       <c r="F15" t="n">
-        <v>0.2304</v>
+        <v>0.2556</v>
       </c>
       <c r="G15" t="n">
-        <v>0.2246</v>
+        <v>0.2848</v>
       </c>
       <c r="H15" t="inlineStr"/>
     </row>
@@ -764,22 +764,22 @@
       </c>
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="n">
-        <v>0.2938</v>
+        <v>0.4158</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2033</v>
+        <v>0.3382</v>
       </c>
       <c r="E19" t="n">
-        <v>0.2762</v>
+        <v>0.3437</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2704</v>
+        <v>0.4413</v>
       </c>
       <c r="G19" t="n">
-        <v>0.2261</v>
+        <v>0.3285</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2839</v>
+        <v>0.3806</v>
       </c>
     </row>
     <row r="20">
@@ -793,16 +793,16 @@
         <v>0.2257</v>
       </c>
       <c r="D20" t="n">
-        <v>0.2679</v>
+        <v>0.2885</v>
       </c>
       <c r="E20" t="n">
         <v>0.2114</v>
       </c>
       <c r="F20" t="n">
-        <v>0.2313</v>
+        <v>0.2771</v>
       </c>
       <c r="G20" t="n">
-        <v>0.2561</v>
+        <v>0.2587</v>
       </c>
       <c r="H20" t="inlineStr"/>
     </row>
@@ -816,13 +816,13 @@
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="n">
-        <v>0.2015</v>
+        <v>0.2483</v>
       </c>
       <c r="F21" t="n">
-        <v>0.2236</v>
+        <v>0.2398</v>
       </c>
       <c r="G21" t="n">
-        <v>0.2143</v>
+        <v>0.2903</v>
       </c>
       <c r="H21" t="inlineStr"/>
     </row>
@@ -870,10 +870,10 @@
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="n">
-        <v>0.2141</v>
+        <v>0.377</v>
       </c>
       <c r="H24" t="n">
-        <v>0.2469</v>
+        <v>0.3751</v>
       </c>
     </row>
     <row r="25">
@@ -884,22 +884,22 @@
       </c>
       <c r="B25" t="inlineStr"/>
       <c r="C25" t="n">
-        <v>0.3661</v>
+        <v>0.4412</v>
       </c>
       <c r="D25" t="n">
-        <v>0.3895</v>
+        <v>0.4604</v>
       </c>
       <c r="E25" t="n">
-        <v>0.3271</v>
+        <v>0.4011</v>
       </c>
       <c r="F25" t="n">
-        <v>0.3482</v>
+        <v>0.4657</v>
       </c>
       <c r="G25" t="n">
-        <v>0.4082</v>
+        <v>0.4514</v>
       </c>
       <c r="H25" t="n">
-        <v>0.3502</v>
+        <v>0.4309</v>
       </c>
     </row>
     <row r="26">
@@ -944,14 +944,14 @@
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="n">
-        <v>0.2138</v>
+        <v>0.2396</v>
       </c>
       <c r="F28" t="n">
         <v>0.216</v>
       </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="n">
-        <v>0.207</v>
+        <v>0.2685</v>
       </c>
     </row>
     <row r="29">
@@ -1038,10 +1038,10 @@
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="n">
-        <v>0.2767</v>
+        <v>0.3831</v>
       </c>
       <c r="H34" t="n">
-        <v>0.2049</v>
+        <v>0.2984</v>
       </c>
     </row>
     <row r="35">
@@ -1054,16 +1054,16 @@
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="n">
-        <v>0.2813</v>
+        <v>0.418</v>
       </c>
       <c r="F35" t="n">
-        <v>0.25</v>
+        <v>0.3567</v>
       </c>
       <c r="G35" t="n">
-        <v>0.2684</v>
+        <v>0.3947</v>
       </c>
       <c r="H35" t="n">
-        <v>0.2544</v>
+        <v>0.3728</v>
       </c>
     </row>
     <row r="36">
@@ -1074,19 +1074,19 @@
       </c>
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="n">
-        <v>0.2563</v>
+        <v>0.3975</v>
       </c>
       <c r="D36" t="n">
-        <v>0.2116</v>
+        <v>0.4018</v>
       </c>
       <c r="E36" t="n">
-        <v>0.2367</v>
+        <v>0.4091</v>
       </c>
       <c r="F36" t="n">
-        <v>0.2281</v>
+        <v>0.3536</v>
       </c>
       <c r="G36" t="n">
-        <v>0.2336</v>
+        <v>0.3888</v>
       </c>
       <c r="H36" t="inlineStr"/>
     </row>
@@ -1170,16 +1170,16 @@
       </c>
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="n">
-        <v>0.2163</v>
+        <v>0.284</v>
       </c>
       <c r="D42" t="n">
-        <v>0.2546</v>
+        <v>0.2733</v>
       </c>
       <c r="E42" t="n">
         <v>0.2586</v>
       </c>
       <c r="F42" t="n">
-        <v>0.2327</v>
+        <v>0.2656</v>
       </c>
       <c r="G42" t="n">
         <v>0.2124</v>
@@ -1194,22 +1194,22 @@
       </c>
       <c r="B43" t="inlineStr"/>
       <c r="C43" t="n">
-        <v>0.207</v>
+        <v>0.2399</v>
       </c>
       <c r="D43" t="n">
-        <v>0.2079</v>
+        <v>0.2524</v>
       </c>
       <c r="E43" t="n">
         <v>0.2257</v>
       </c>
       <c r="F43" t="n">
-        <v>0.2028</v>
+        <v>0.3191</v>
       </c>
       <c r="G43" t="n">
-        <v>0.2385</v>
+        <v>0.2966</v>
       </c>
       <c r="H43" t="n">
-        <v>0.2441</v>
+        <v>0.3301</v>
       </c>
     </row>
     <row r="44">
@@ -1235,13 +1235,13 @@
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="n">
-        <v>0.2363</v>
+        <v>0.2751</v>
       </c>
       <c r="E45" t="n">
-        <v>0.2242</v>
+        <v>0.3047</v>
       </c>
       <c r="F45" t="n">
-        <v>0.2121</v>
+        <v>0.2606</v>
       </c>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr"/>
@@ -1302,13 +1302,13 @@
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="n">
-        <v>0.2304</v>
+        <v>0.2408</v>
       </c>
       <c r="F49" t="n">
-        <v>0.2413</v>
+        <v>0.2669</v>
       </c>
       <c r="G49" t="n">
-        <v>0.2148</v>
+        <v>0.2411</v>
       </c>
       <c r="H49" t="inlineStr"/>
     </row>
@@ -1322,7 +1322,7 @@
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="n">
-        <v>0.2011</v>
+        <v>0.2425</v>
       </c>
       <c r="F50" t="n">
         <v>0.2219</v>
@@ -1331,7 +1331,7 @@
         <v>0.2255</v>
       </c>
       <c r="H50" t="n">
-        <v>0.2292</v>
+        <v>0.2325</v>
       </c>
     </row>
     <row r="51">
@@ -1370,7 +1370,7 @@
         <v>0.229</v>
       </c>
       <c r="E52" t="n">
-        <v>0.2201</v>
+        <v>0.2653</v>
       </c>
       <c r="F52" t="n">
         <v>0.2078</v>
@@ -1388,16 +1388,16 @@
       </c>
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="n">
-        <v>0.2646</v>
+        <v>0.2946</v>
       </c>
       <c r="D53" t="n">
-        <v>0.2829</v>
+        <v>0.3122</v>
       </c>
       <c r="E53" t="n">
-        <v>0.2045</v>
+        <v>0.2527</v>
       </c>
       <c r="F53" t="n">
-        <v>0.221</v>
+        <v>0.2558</v>
       </c>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr"/>
@@ -1410,16 +1410,16 @@
       </c>
       <c r="B54" t="inlineStr"/>
       <c r="C54" t="n">
-        <v>0.258</v>
+        <v>0.2654</v>
       </c>
       <c r="D54" t="n">
-        <v>0.2071</v>
+        <v>0.2126</v>
       </c>
       <c r="E54" t="n">
-        <v>0.2132</v>
+        <v>0.2878</v>
       </c>
       <c r="F54" t="n">
-        <v>0.2675</v>
+        <v>0.286</v>
       </c>
       <c r="G54" t="n">
         <v>0.2748</v>
@@ -1434,19 +1434,19 @@
       </c>
       <c r="B55" t="inlineStr"/>
       <c r="C55" t="n">
-        <v>0.2486</v>
+        <v>0.302</v>
       </c>
       <c r="D55" t="n">
-        <v>0.2386</v>
+        <v>0.3305</v>
       </c>
       <c r="E55" t="n">
-        <v>0.2492</v>
+        <v>0.3508</v>
       </c>
       <c r="F55" t="n">
-        <v>0.2349</v>
+        <v>0.2807</v>
       </c>
       <c r="G55" t="n">
-        <v>0.2429</v>
+        <v>0.3425</v>
       </c>
       <c r="H55" t="inlineStr"/>
     </row>
@@ -1464,13 +1464,13 @@
         <v>0.2173</v>
       </c>
       <c r="E56" t="n">
-        <v>0.2219</v>
+        <v>0.2677</v>
       </c>
       <c r="F56" t="n">
-        <v>0.2195</v>
+        <v>0.2761</v>
       </c>
       <c r="G56" t="n">
-        <v>0.2114</v>
+        <v>0.3187</v>
       </c>
       <c r="H56" t="inlineStr"/>
     </row>
@@ -1485,16 +1485,16 @@
         <v>0.2649</v>
       </c>
       <c r="D57" t="n">
-        <v>0.2435</v>
+        <v>0.3547</v>
       </c>
       <c r="E57" t="n">
-        <v>0.2366</v>
+        <v>0.322</v>
       </c>
       <c r="F57" t="n">
-        <v>0.2552</v>
+        <v>0.3471</v>
       </c>
       <c r="G57" t="n">
-        <v>0.2011</v>
+        <v>0.294</v>
       </c>
       <c r="H57" t="inlineStr"/>
     </row>
@@ -1506,7 +1506,7 @@
       </c>
       <c r="B58" t="inlineStr"/>
       <c r="C58" t="n">
-        <v>0.2049</v>
+        <v>0.2487</v>
       </c>
       <c r="D58" t="n">
         <v>0.2633</v>
@@ -1529,22 +1529,22 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.2109</v>
+        <v>0.354</v>
       </c>
       <c r="C59" t="n">
-        <v>0.2541</v>
+        <v>0.4725</v>
       </c>
       <c r="D59" t="n">
-        <v>0.2363</v>
+        <v>0.4009</v>
       </c>
       <c r="E59" t="n">
-        <v>0.2515</v>
+        <v>0.3542</v>
       </c>
       <c r="F59" t="n">
-        <v>0.2424</v>
+        <v>0.367</v>
       </c>
       <c r="G59" t="n">
-        <v>0.2632</v>
+        <v>0.2764</v>
       </c>
       <c r="H59" t="inlineStr"/>
     </row>
@@ -1555,16 +1555,16 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.2042</v>
+        <v>0.4124</v>
       </c>
       <c r="C60" t="n">
-        <v>0.2832</v>
+        <v>0.5389</v>
       </c>
       <c r="D60" t="n">
-        <v>0.2866</v>
+        <v>0.5381</v>
       </c>
       <c r="E60" t="n">
-        <v>0.2326</v>
+        <v>0.3734</v>
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="n">
@@ -1579,20 +1579,20 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.2145</v>
+        <v>0.2707</v>
       </c>
       <c r="C61" t="n">
-        <v>0.2571</v>
+        <v>0.5066000000000001</v>
       </c>
       <c r="D61" t="n">
-        <v>0.2393</v>
+        <v>0.4096</v>
       </c>
       <c r="E61" t="n">
-        <v>0.2513</v>
+        <v>0.2893</v>
       </c>
       <c r="F61" t="inlineStr"/>
       <c r="G61" t="n">
-        <v>0.2046</v>
+        <v>0.2136</v>
       </c>
       <c r="H61" t="inlineStr"/>
     </row>
@@ -1604,13 +1604,13 @@
       </c>
       <c r="B62" t="inlineStr"/>
       <c r="C62" t="n">
-        <v>0.2191</v>
+        <v>0.2548</v>
       </c>
       <c r="D62" t="n">
         <v>0.2444</v>
       </c>
       <c r="E62" t="n">
-        <v>0.2353</v>
+        <v>0.2466</v>
       </c>
       <c r="F62" t="n">
         <v>0.2383</v>
@@ -1693,7 +1693,7 @@
       <c r="B67" t="inlineStr"/>
       <c r="C67" t="inlineStr"/>
       <c r="D67" t="n">
-        <v>0.258</v>
+        <v>0.2719</v>
       </c>
       <c r="E67" t="n">
         <v>0.3554</v>
@@ -1712,19 +1712,19 @@
       </c>
       <c r="B68" t="inlineStr"/>
       <c r="C68" t="n">
-        <v>0.2039</v>
+        <v>0.4353</v>
       </c>
       <c r="D68" t="n">
-        <v>0.217</v>
+        <v>0.3764</v>
       </c>
       <c r="E68" t="n">
-        <v>0.2788</v>
+        <v>0.4512</v>
       </c>
       <c r="F68" t="n">
-        <v>0.329</v>
+        <v>0.4856</v>
       </c>
       <c r="G68" t="n">
-        <v>0.2466</v>
+        <v>0.3965</v>
       </c>
       <c r="H68" t="inlineStr"/>
     </row>
@@ -1736,16 +1736,16 @@
       </c>
       <c r="B69" t="inlineStr"/>
       <c r="C69" t="n">
-        <v>0.2208</v>
+        <v>0.404</v>
       </c>
       <c r="D69" t="n">
-        <v>0.202</v>
+        <v>0.5175999999999999</v>
       </c>
       <c r="E69" t="n">
-        <v>0.2579</v>
+        <v>0.4553</v>
       </c>
       <c r="F69" t="n">
-        <v>0.2346</v>
+        <v>0.4286</v>
       </c>
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr"/>
@@ -1758,16 +1758,16 @@
       </c>
       <c r="B70" t="inlineStr"/>
       <c r="C70" t="n">
-        <v>0.2098</v>
+        <v>0.307</v>
       </c>
       <c r="D70" t="n">
-        <v>0.2036</v>
+        <v>0.2981</v>
       </c>
       <c r="E70" t="n">
-        <v>0.2248</v>
+        <v>0.3851</v>
       </c>
       <c r="F70" t="n">
-        <v>0.2121</v>
+        <v>0.3842</v>
       </c>
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr"/>
@@ -1780,22 +1780,22 @@
       </c>
       <c r="B71" t="inlineStr"/>
       <c r="C71" t="n">
-        <v>0.2013</v>
+        <v>0.2553</v>
       </c>
       <c r="D71" t="n">
-        <v>0.2015</v>
+        <v>0.2535</v>
       </c>
       <c r="E71" t="n">
-        <v>0.2778</v>
+        <v>0.3114</v>
       </c>
       <c r="F71" t="n">
-        <v>0.2564</v>
+        <v>0.292</v>
       </c>
       <c r="G71" t="n">
-        <v>0.2069</v>
+        <v>0.2893</v>
       </c>
       <c r="H71" t="n">
-        <v>0.2012</v>
+        <v>0.3207</v>
       </c>
     </row>
     <row r="72">
@@ -1806,19 +1806,19 @@
       </c>
       <c r="B72" t="inlineStr"/>
       <c r="C72" t="n">
-        <v>0.2158</v>
+        <v>0.3238</v>
       </c>
       <c r="D72" t="n">
-        <v>0.2487</v>
+        <v>0.3405</v>
       </c>
       <c r="E72" t="n">
-        <v>0.2185</v>
+        <v>0.3129</v>
       </c>
       <c r="F72" t="n">
-        <v>0.2236</v>
+        <v>0.3523</v>
       </c>
       <c r="G72" t="n">
-        <v>0.2241</v>
+        <v>0.3414</v>
       </c>
       <c r="H72" t="inlineStr"/>
     </row>
@@ -1830,19 +1830,19 @@
       </c>
       <c r="B73" t="inlineStr"/>
       <c r="C73" t="n">
-        <v>0.2088</v>
+        <v>0.2827</v>
       </c>
       <c r="D73" t="n">
-        <v>0.2071</v>
+        <v>0.2771</v>
       </c>
       <c r="E73" t="n">
-        <v>0.2033</v>
+        <v>0.3328</v>
       </c>
       <c r="F73" t="n">
-        <v>0.2005</v>
+        <v>0.2599</v>
       </c>
       <c r="G73" t="n">
-        <v>0.2248</v>
+        <v>0.2483</v>
       </c>
       <c r="H73" t="inlineStr"/>
     </row>
@@ -1860,7 +1860,7 @@
         <v>0.2246</v>
       </c>
       <c r="E74" t="n">
-        <v>0.208</v>
+        <v>0.3112</v>
       </c>
       <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr"/>
@@ -1874,19 +1874,19 @@
       </c>
       <c r="B75" t="inlineStr"/>
       <c r="C75" t="n">
-        <v>0.2831</v>
+        <v>0.4961</v>
       </c>
       <c r="D75" t="n">
-        <v>0.256</v>
+        <v>0.5793</v>
       </c>
       <c r="E75" t="n">
-        <v>0.2855</v>
+        <v>0.5601</v>
       </c>
       <c r="F75" t="n">
-        <v>0.2638</v>
+        <v>0.4664</v>
       </c>
       <c r="G75" t="n">
-        <v>0.2684</v>
+        <v>0.4847</v>
       </c>
       <c r="H75" t="inlineStr"/>
     </row>
@@ -1898,13 +1898,13 @@
       </c>
       <c r="B76" t="inlineStr"/>
       <c r="C76" t="n">
-        <v>0.2003</v>
+        <v>0.3231</v>
       </c>
       <c r="D76" t="n">
         <v>0.2455</v>
       </c>
       <c r="E76" t="n">
-        <v>0.2062</v>
+        <v>0.264</v>
       </c>
       <c r="F76" t="n">
         <v>0.2148</v>
@@ -1920,10 +1920,10 @@
       </c>
       <c r="B77" t="inlineStr"/>
       <c r="C77" t="n">
-        <v>0.202</v>
+        <v>0.323</v>
       </c>
       <c r="D77" t="n">
-        <v>0.2793</v>
+        <v>0.3276</v>
       </c>
       <c r="E77" t="n">
         <v>0.2603</v>
@@ -1980,16 +1980,16 @@
       </c>
       <c r="B80" t="inlineStr"/>
       <c r="C80" t="n">
-        <v>0.2403</v>
+        <v>0.257</v>
       </c>
       <c r="D80" t="n">
-        <v>0.2678</v>
+        <v>0.2696</v>
       </c>
       <c r="E80" t="n">
-        <v>0.2253</v>
+        <v>0.3218</v>
       </c>
       <c r="F80" t="n">
-        <v>0.2072</v>
+        <v>0.2446</v>
       </c>
       <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr"/>
@@ -2002,19 +2002,19 @@
       </c>
       <c r="B81" t="inlineStr"/>
       <c r="C81" t="n">
-        <v>0.2288</v>
+        <v>0.3306</v>
       </c>
       <c r="D81" t="n">
-        <v>0.2003</v>
+        <v>0.4435</v>
       </c>
       <c r="E81" t="n">
-        <v>0.2305</v>
+        <v>0.4625</v>
       </c>
       <c r="F81" t="n">
-        <v>0.2063</v>
+        <v>0.4342</v>
       </c>
       <c r="G81" t="n">
-        <v>0.2219</v>
+        <v>0.3679</v>
       </c>
       <c r="H81" t="inlineStr"/>
     </row>
@@ -2026,19 +2026,19 @@
       </c>
       <c r="B82" t="inlineStr"/>
       <c r="C82" t="n">
-        <v>0.208</v>
+        <v>0.2247</v>
       </c>
       <c r="D82" t="n">
-        <v>0.2056</v>
+        <v>0.3231</v>
       </c>
       <c r="E82" t="n">
-        <v>0.2193</v>
+        <v>0.3226</v>
       </c>
       <c r="F82" t="n">
         <v>0.3142</v>
       </c>
       <c r="G82" t="n">
-        <v>0.2215</v>
+        <v>0.3124</v>
       </c>
       <c r="H82" t="inlineStr"/>
     </row>
@@ -2090,7 +2090,7 @@
         <v>0.2025</v>
       </c>
       <c r="G85" t="n">
-        <v>0.2228</v>
+        <v>0.266</v>
       </c>
       <c r="H85" t="inlineStr"/>
     </row>
@@ -2101,19 +2101,19 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.2506</v>
+        <v>0.3745</v>
       </c>
       <c r="C86" t="n">
-        <v>0.2559</v>
+        <v>0.3735</v>
       </c>
       <c r="D86" t="n">
-        <v>0.2056</v>
+        <v>0.341</v>
       </c>
       <c r="E86" t="n">
-        <v>0.298</v>
+        <v>0.4291</v>
       </c>
       <c r="F86" t="n">
-        <v>0.2958</v>
+        <v>0.3882</v>
       </c>
       <c r="G86" t="inlineStr"/>
       <c r="H86" t="inlineStr"/>
@@ -2175,7 +2175,7 @@
       <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr"/>
       <c r="F90" t="n">
-        <v>0.2236</v>
+        <v>0.258</v>
       </c>
       <c r="G90" t="n">
         <v>0.2196</v>
@@ -2190,16 +2190,16 @@
       </c>
       <c r="B91" t="inlineStr"/>
       <c r="C91" t="n">
-        <v>0.2316</v>
+        <v>0.2369</v>
       </c>
       <c r="D91" t="n">
-        <v>0.2219</v>
+        <v>0.2282</v>
       </c>
       <c r="E91" t="n">
-        <v>0.2073</v>
+        <v>0.2414</v>
       </c>
       <c r="F91" t="n">
-        <v>0.2228</v>
+        <v>0.251</v>
       </c>
       <c r="G91" t="inlineStr"/>
       <c r="H91" t="inlineStr"/>
@@ -2211,19 +2211,19 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.2459</v>
+        <v>0.3168</v>
       </c>
       <c r="C92" t="n">
-        <v>0.2045</v>
+        <v>0.285</v>
       </c>
       <c r="D92" t="n">
-        <v>0.2349</v>
+        <v>0.3089</v>
       </c>
       <c r="E92" t="n">
-        <v>0.2768</v>
+        <v>0.3395</v>
       </c>
       <c r="F92" t="n">
-        <v>0.2102</v>
+        <v>0.3441</v>
       </c>
       <c r="G92" t="inlineStr"/>
       <c r="H92" t="inlineStr"/>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="B93" t="inlineStr"/>
       <c r="C93" t="n">
-        <v>0.253</v>
+        <v>0.3072</v>
       </c>
       <c r="D93" t="n">
         <v>0.2358</v>
@@ -2245,7 +2245,7 @@
         <v>0.2642</v>
       </c>
       <c r="F93" t="n">
-        <v>0.2317</v>
+        <v>0.2582</v>
       </c>
       <c r="G93" t="inlineStr"/>
       <c r="H93" t="inlineStr"/>
@@ -2257,19 +2257,19 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.2221</v>
+        <v>0.3099</v>
       </c>
       <c r="C94" t="n">
-        <v>0.2012</v>
+        <v>0.2441</v>
       </c>
       <c r="D94" t="n">
-        <v>0.2585</v>
+        <v>0.3643</v>
       </c>
       <c r="E94" t="n">
-        <v>0.2609</v>
+        <v>0.3601</v>
       </c>
       <c r="F94" t="n">
-        <v>0.2187</v>
+        <v>0.3732</v>
       </c>
       <c r="G94" t="inlineStr"/>
       <c r="H94" t="inlineStr"/>
@@ -2339,7 +2339,7 @@
         <v>0.2113</v>
       </c>
       <c r="D98" t="n">
-        <v>0.218</v>
+        <v>0.2283</v>
       </c>
       <c r="E98" t="inlineStr"/>
       <c r="F98" t="inlineStr"/>
@@ -2354,19 +2354,19 @@
       </c>
       <c r="B99" t="inlineStr"/>
       <c r="C99" t="n">
-        <v>0.2328</v>
+        <v>0.4001</v>
       </c>
       <c r="D99" t="n">
-        <v>0.2454</v>
+        <v>0.3367</v>
       </c>
       <c r="E99" t="n">
-        <v>0.2669</v>
+        <v>0.3736</v>
       </c>
       <c r="F99" t="n">
-        <v>0.2928</v>
+        <v>0.334</v>
       </c>
       <c r="G99" t="n">
-        <v>0.2448</v>
+        <v>0.4416</v>
       </c>
       <c r="H99" t="inlineStr"/>
     </row>
@@ -2385,7 +2385,7 @@
         <v>0.2118</v>
       </c>
       <c r="F100" t="n">
-        <v>0.2207</v>
+        <v>0.257</v>
       </c>
       <c r="G100" t="inlineStr"/>
       <c r="H100" t="inlineStr"/>
@@ -2398,19 +2398,19 @@
       </c>
       <c r="B101" t="inlineStr"/>
       <c r="C101" t="n">
-        <v>0.2049</v>
+        <v>0.308</v>
       </c>
       <c r="D101" t="n">
-        <v>0.3074</v>
+        <v>0.358</v>
       </c>
       <c r="E101" t="n">
-        <v>0.2162</v>
+        <v>0.3561</v>
       </c>
       <c r="F101" t="n">
-        <v>0.2053</v>
+        <v>0.2534</v>
       </c>
       <c r="G101" t="n">
-        <v>0.2039</v>
+        <v>0.3209</v>
       </c>
       <c r="H101" t="n">
         <v>0.2212</v>
@@ -2442,13 +2442,13 @@
         <v>0.2958</v>
       </c>
       <c r="E103" t="n">
-        <v>0.2495</v>
+        <v>0.3128</v>
       </c>
       <c r="F103" t="n">
-        <v>0.2382</v>
+        <v>0.3288</v>
       </c>
       <c r="G103" t="n">
-        <v>0.2547</v>
+        <v>0.314</v>
       </c>
       <c r="H103" t="inlineStr"/>
     </row>
@@ -2461,7 +2461,7 @@
       <c r="B104" t="inlineStr"/>
       <c r="C104" t="inlineStr"/>
       <c r="D104" t="n">
-        <v>0.218</v>
+        <v>0.3335</v>
       </c>
       <c r="E104" t="n">
         <v>0.2146</v>
@@ -2485,7 +2485,7 @@
       <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr"/>
       <c r="F105" t="n">
-        <v>0.218</v>
+        <v>0.2189</v>
       </c>
       <c r="G105" t="n">
         <v>0.2045</v>
@@ -2560,7 +2560,7 @@
       </c>
       <c r="B109" t="inlineStr"/>
       <c r="C109" t="n">
-        <v>0.2184</v>
+        <v>0.2277</v>
       </c>
       <c r="D109" t="n">
         <v>0.2635</v>
@@ -2586,7 +2586,7 @@
       <c r="E110" t="inlineStr"/>
       <c r="F110" t="inlineStr"/>
       <c r="G110" t="n">
-        <v>0.2968</v>
+        <v>0.317</v>
       </c>
       <c r="H110" t="inlineStr"/>
     </row>
@@ -2597,7 +2597,7 @@
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.2213</v>
+        <v>0.2277</v>
       </c>
       <c r="C111" t="n">
         <v>0.2021</v>
@@ -2605,7 +2605,7 @@
       <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr"/>
       <c r="F111" t="n">
-        <v>0.2301</v>
+        <v>0.3383</v>
       </c>
       <c r="G111" t="n">
         <v>0.2995</v>
@@ -2642,10 +2642,10 @@
         <v>0.2121</v>
       </c>
       <c r="E113" t="n">
-        <v>0.2183</v>
+        <v>0.2192</v>
       </c>
       <c r="F113" t="n">
-        <v>0.2037</v>
+        <v>0.3017</v>
       </c>
       <c r="G113" t="inlineStr"/>
       <c r="H113" t="inlineStr"/>
@@ -2704,13 +2704,13 @@
       </c>
       <c r="B117" t="inlineStr"/>
       <c r="C117" t="n">
-        <v>0.2191</v>
+        <v>0.2925</v>
       </c>
       <c r="D117" t="n">
         <v>0.2698</v>
       </c>
       <c r="E117" t="n">
-        <v>0.2345</v>
+        <v>0.3109</v>
       </c>
       <c r="F117" t="n">
         <v>0.2354</v>
@@ -2753,7 +2753,7 @@
         <v>0.2528</v>
       </c>
       <c r="F119" t="n">
-        <v>0.274</v>
+        <v>0.2788</v>
       </c>
       <c r="G119" t="n">
         <v>0.2473</v>
@@ -2836,10 +2836,10 @@
       <c r="C124" t="inlineStr"/>
       <c r="D124" t="inlineStr"/>
       <c r="E124" t="n">
-        <v>0.2011</v>
+        <v>0.227</v>
       </c>
       <c r="F124" t="n">
-        <v>0.2554</v>
+        <v>0.2619</v>
       </c>
       <c r="G124" t="inlineStr"/>
       <c r="H124" t="inlineStr"/>
@@ -2989,7 +2989,7 @@
       <c r="B134" t="inlineStr"/>
       <c r="C134" t="inlineStr"/>
       <c r="D134" t="n">
-        <v>0.2095</v>
+        <v>0.3114</v>
       </c>
       <c r="E134" t="inlineStr"/>
       <c r="F134" t="inlineStr"/>
@@ -3069,10 +3069,10 @@
         <v>0.3655</v>
       </c>
       <c r="F138" t="n">
-        <v>0.3155</v>
+        <v>0.3158</v>
       </c>
       <c r="G138" t="n">
-        <v>0.2851</v>
+        <v>0.3641</v>
       </c>
       <c r="H138" t="inlineStr"/>
     </row>
@@ -3133,20 +3133,20 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.2066</v>
+        <v>0.294</v>
       </c>
       <c r="C142" t="n">
-        <v>0.2077</v>
+        <v>0.3024</v>
       </c>
       <c r="D142" t="n">
-        <v>0.2456</v>
+        <v>0.266</v>
       </c>
       <c r="E142" t="n">
-        <v>0.286</v>
+        <v>0.3098</v>
       </c>
       <c r="F142" t="inlineStr"/>
       <c r="G142" t="n">
-        <v>0.2815</v>
+        <v>0.3049</v>
       </c>
       <c r="H142" t="inlineStr"/>
     </row>
@@ -3160,16 +3160,16 @@
       <c r="C143" t="inlineStr"/>
       <c r="D143" t="inlineStr"/>
       <c r="E143" t="n">
-        <v>0.2767</v>
+        <v>0.3976</v>
       </c>
       <c r="F143" t="n">
-        <v>0.2897</v>
+        <v>0.3978</v>
       </c>
       <c r="G143" t="n">
-        <v>0.2957</v>
+        <v>0.4116</v>
       </c>
       <c r="H143" t="n">
-        <v>0.2972</v>
+        <v>0.3876</v>
       </c>
     </row>
     <row r="144">
@@ -3181,13 +3181,13 @@
       <c r="B144" t="inlineStr"/>
       <c r="C144" t="inlineStr"/>
       <c r="D144" t="n">
-        <v>0.2869</v>
+        <v>0.4693</v>
       </c>
       <c r="E144" t="n">
-        <v>0.2232</v>
+        <v>0.4337</v>
       </c>
       <c r="F144" t="n">
-        <v>0.2415</v>
+        <v>0.4839</v>
       </c>
       <c r="G144" t="n">
         <v>0.399</v>
@@ -3264,13 +3264,13 @@
       </c>
       <c r="B148" t="inlineStr"/>
       <c r="C148" t="n">
-        <v>0.2024</v>
+        <v>0.2079</v>
       </c>
       <c r="D148" t="n">
-        <v>0.2141</v>
+        <v>0.2607</v>
       </c>
       <c r="E148" t="n">
-        <v>0.2488</v>
+        <v>0.3191</v>
       </c>
       <c r="F148" t="n">
         <v>0.2013</v>
